--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,98 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,8 +760,11 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -831,8 +834,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +908,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,65 +1012,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E12" s="3">
         <v>13300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4100</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1213,8 +1232,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E17" s="3">
         <v>18100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,8 +1405,11 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1388,56 +1417,56 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-20800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1509,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,23 +1519,23 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1000</v>
       </c>
       <c r="G20" s="3">
         <v>1000</v>
       </c>
       <c r="H20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1510,32 +1543,32 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>200</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1581,11 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,56 +1593,56 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-15400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-17200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-19600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1655,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1690,65 +1729,68 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-11100</v>
       </c>
       <c r="O23" s="3">
         <v>-11100</v>
       </c>
       <c r="P23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1832,8 +1877,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-11100</v>
       </c>
       <c r="O26" s="3">
         <v>-11100</v>
       </c>
       <c r="P26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-11100</v>
       </c>
       <c r="O27" s="3">
         <v>-11100</v>
       </c>
       <c r="P27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2395,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2338,23 +2407,23 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1000</v>
       </c>
       <c r="G32" s="3">
         <v>-1000</v>
       </c>
       <c r="H32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2362,32 +2431,32 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-11100</v>
       </c>
       <c r="O33" s="3">
         <v>-11100</v>
       </c>
       <c r="P33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-11100</v>
       </c>
       <c r="O35" s="3">
         <v>-11100</v>
       </c>
       <c r="P35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,59 +2828,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E41" s="3">
         <v>46900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,59 +2900,62 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E42" s="3">
         <v>145500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>81900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>95000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>97400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>88900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>65800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>88500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>98100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>111200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>128600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>119700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>99600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>18900</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,13 +2974,16 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>400</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2899,8 +2991,8 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>100</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -2909,10 +3001,10 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -2924,19 +3016,19 @@
         <v>100</v>
       </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2956,8 +3048,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3027,59 +3122,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E45" s="3">
         <v>8400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,59 +3196,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>196300</v>
+      </c>
+      <c r="E46" s="3">
         <v>200900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>143600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>134100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>131400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>145900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>153700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>100600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>115300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>130600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>141000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>148000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>151000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>164000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>64700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3205,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>2500</v>
-      </c>
-      <c r="O47" s="3">
-        <v>12200</v>
       </c>
       <c r="P47" s="3">
         <v>12200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>12200</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3231,8 +3335,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3240,59 +3344,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,8 +3418,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3640,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3533,7 +3652,7 @@
         <v>2000</v>
       </c>
       <c r="E52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="F52" s="3">
         <v>4200</v>
@@ -3551,32 +3670,32 @@
         <v>4200</v>
       </c>
       <c r="K52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L52" s="3">
         <v>3800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>2400</v>
       </c>
       <c r="M52" s="3">
         <v>2400</v>
       </c>
       <c r="N52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3788,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E54" s="3">
         <v>205700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>141800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>139200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>154000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>162000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>123500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>148300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>158900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>169400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>179000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,59 +3920,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
         <v>2000</v>
       </c>
       <c r="F57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +3992,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3933,59 +4066,62 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E59" s="3">
         <v>10300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,59 +4140,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E60" s="3">
         <v>12300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,28 +4214,31 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E61" s="3">
         <v>32100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>4100</v>
       </c>
       <c r="H61" s="3">
         <v>4100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -4146,56 +4288,59 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1300</v>
       </c>
       <c r="P62" s="3">
         <v>1300</v>
       </c>
       <c r="Q62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,8 +4353,8 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4217,8 +4362,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4584,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E66" s="3">
         <v>45500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>10000</v>
       </c>
       <c r="N66" s="3">
         <v>10000</v>
       </c>
       <c r="O66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="P66" s="3">
         <v>11300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,14 +4882,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>111600</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>77900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4982,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-285900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-264400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-247700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-232200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-214800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-196200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-179800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-164600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-147700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-128900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-114700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-102100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-91100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-51900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-42400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5278,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>140500</v>
+      </c>
+      <c r="E76" s="3">
         <v>160200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>105600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>103300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>134800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>149200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>94200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>126000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>138300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>148900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>158100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>167900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-50000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-40800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-11100</v>
       </c>
       <c r="O81" s="3">
         <v>-11100</v>
       </c>
       <c r="P81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5609,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5451,11 +5649,11 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5463,13 +5661,13 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5483,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,52 +6155,53 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -5990,10 +6210,10 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6007,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>13100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-99700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E100" s="3">
         <v>69700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>23600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>68300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>118900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>31900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>23000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>22900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,26 +6847,29 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
@@ -6631,8 +6879,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -6646,8 +6894,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6673,65 +6921,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>6100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>29200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,8 +764,11 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -837,8 +841,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -911,8 +918,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,68 +1026,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E12" s="3">
         <v>18000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4100</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,8 +1178,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,8 +1255,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,68 +1360,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E17" s="3">
         <v>22800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1435,11 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1417,59 +1447,59 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-18100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,8 +1543,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1519,26 +1553,26 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1000</v>
       </c>
       <c r="H20" s="3">
         <v>1000</v>
       </c>
       <c r="I20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1546,32 +1580,32 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,8 +1618,11 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1593,59 +1630,59 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-16400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-19600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,31 +1695,34 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1732,68 +1772,71 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-11100</v>
       </c>
       <c r="P23" s="3">
         <v>-11100</v>
       </c>
       <c r="Q23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R23" s="3">
         <v>-28100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,8 +1849,11 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,68 +2003,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-11100</v>
       </c>
       <c r="P26" s="3">
         <v>-11100</v>
       </c>
       <c r="Q26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R26" s="3">
         <v>-28100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,68 +2080,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-11100</v>
       </c>
       <c r="P27" s="3">
         <v>-11100</v>
       </c>
       <c r="Q27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R27" s="3">
         <v>-28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,8 +2465,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2407,26 +2477,26 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1000</v>
       </c>
       <c r="H32" s="3">
         <v>-1000</v>
       </c>
       <c r="I32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2434,32 +2504,32 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,68 +2542,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-11100</v>
       </c>
       <c r="P33" s="3">
         <v>-11100</v>
       </c>
       <c r="Q33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R33" s="3">
         <v>-28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,68 +2696,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-11100</v>
       </c>
       <c r="P35" s="3">
         <v>-11100</v>
       </c>
       <c r="Q35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R35" s="3">
         <v>-28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,62 +2915,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E41" s="3">
         <v>34600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>44000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,62 +2990,65 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E42" s="3">
         <v>154000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>81900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>95000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>97400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>88900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>65800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>88500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>111200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>128600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>119700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>99600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18900</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,25 +3067,28 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>100</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -3004,10 +3097,10 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3019,19 +3112,19 @@
         <v>100</v>
       </c>
       <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -3051,8 +3144,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3125,62 +3221,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E45" s="3">
         <v>7300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,62 +3298,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E46" s="3">
         <v>196300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>143600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>134100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>131400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>145900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>153700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>100600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>115300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>130600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>141000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>148000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>151000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>164000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>64700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>41300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3312,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>2500</v>
-      </c>
-      <c r="P47" s="3">
-        <v>12200</v>
       </c>
       <c r="Q47" s="3">
         <v>12200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>12200</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3338,8 +3443,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3347,62 +3452,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,8 +3529,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,19 +3760,22 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
       </c>
       <c r="F52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="3">
         <v>4200</v>
@@ -3673,32 +3793,32 @@
         <v>4200</v>
       </c>
       <c r="L52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M52" s="3">
         <v>3800</v>
-      </c>
-      <c r="M52" s="3">
-        <v>2400</v>
       </c>
       <c r="N52" s="3">
         <v>2400</v>
       </c>
       <c r="O52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P52" s="3">
         <v>3300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,62 +3914,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>176900</v>
+      </c>
+      <c r="E54" s="3">
         <v>200800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>205700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>150900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>141800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>139200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>154000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>162000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>123500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>137700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>148300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>158900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>169400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>179000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,62 +4051,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>2000</v>
       </c>
       <c r="F57" s="3">
         <v>2000</v>
       </c>
       <c r="G57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4126,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4069,62 +4203,65 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E59" s="3">
         <v>13500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,62 +4280,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E60" s="3">
         <v>14700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,31 +4357,34 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E61" s="3">
         <v>44800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>4100</v>
       </c>
       <c r="I61" s="3">
         <v>4100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4291,59 +4434,62 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1300</v>
       </c>
       <c r="Q62" s="3">
         <v>1300</v>
       </c>
       <c r="R62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4356,8 +4502,8 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,62 +4742,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E66" s="3">
         <v>60400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>10000</v>
       </c>
       <c r="O66" s="3">
         <v>10000</v>
       </c>
       <c r="P66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Q66" s="3">
         <v>11300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4885,14 +5053,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>111600</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>77900</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,62 +5156,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-309300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-285900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-264400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-247700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-232200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-214800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-196200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-179800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-164600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-147700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-114700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-102100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-91100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-80000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-51900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-42400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,62 +5464,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E76" s="3">
         <v>140500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>160200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>105600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>103300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>118400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>134800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>149200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>94200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>138300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>158100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>167900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-50000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-40800</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,68 +5700,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-11100</v>
       </c>
       <c r="P81" s="3">
         <v>-11100</v>
       </c>
       <c r="Q81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="R81" s="3">
         <v>-28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,8 +5808,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5652,11 +5851,11 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -5664,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,68 +6268,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,55 +6376,56 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
@@ -6213,10 +6434,10 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,68 +6605,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>22600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-99700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>12500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>69700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>23600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>20100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>68300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>118900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>31900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>23000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>22900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,29 +7096,32 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -6882,8 +7131,8 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -6897,8 +7146,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -6924,68 +7173,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>29200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,105 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -844,8 +848,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -921,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1040,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E12" s="3">
         <v>19100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4100</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1258,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1387,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E17" s="3">
         <v>24300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,8 +1465,11 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1447,62 +1477,62 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-22800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-20800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1577,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1553,29 +1587,29 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1000</v>
       </c>
       <c r="I20" s="3">
         <v>1000</v>
       </c>
       <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1583,32 +1617,32 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>200</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>200</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1655,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1630,62 +1667,62 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-21300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-28100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-19600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,17 +1735,20 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1724,8 +1764,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1775,71 +1815,74 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q23" s="3">
         <v>-11100</v>
       </c>
       <c r="R23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-28100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-19700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,8 +1895,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2055,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q26" s="3">
         <v>-11100</v>
       </c>
       <c r="R26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S26" s="3">
         <v>-28100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-19700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2135,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q27" s="3">
         <v>-11100</v>
       </c>
       <c r="R27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S27" s="3">
         <v>-28100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-19700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,8 +2535,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2477,29 +2547,29 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1000</v>
       </c>
       <c r="I32" s="3">
         <v>-1000</v>
       </c>
       <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2507,32 +2577,32 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-200</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,71 +2615,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q33" s="3">
         <v>-11100</v>
       </c>
       <c r="R33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S33" s="3">
         <v>-28100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-19700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2775,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q35" s="3">
         <v>-11100</v>
       </c>
       <c r="R35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S35" s="3">
         <v>-28100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-19700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2855,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E41" s="3">
         <v>20600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,65 +3080,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E42" s="3">
         <v>145500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>145500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>81900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>95000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>88900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>65800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>98100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>111200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>128600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>119700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>99600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>18900</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3070,28 +3160,31 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>100</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3100,10 +3193,10 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -3115,19 +3208,19 @@
         <v>100</v>
       </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3224,65 +3320,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E45" s="3">
         <v>8200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E46" s="3">
         <v>174300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>196300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>143600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>134100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>131400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>145900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>153700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>100600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>115300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>130600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>141000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>148000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>151000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>164000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>64700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>41300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3420,16 +3525,16 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>12200</v>
       </c>
       <c r="R47" s="3">
         <v>12200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>12200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3446,8 +3551,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3455,65 +3560,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,22 +3880,25 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2000</v>
       </c>
       <c r="F52" s="3">
         <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="3">
         <v>4200</v>
@@ -3796,32 +3916,32 @@
         <v>4200</v>
       </c>
       <c r="M52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N52" s="3">
         <v>3800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>2400</v>
       </c>
       <c r="O52" s="3">
         <v>2400</v>
       </c>
       <c r="P52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E54" s="3">
         <v>176900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>200800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>205700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>150900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>141800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>139200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>154000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>162000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>108900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>123500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>148300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>158900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>169400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>179000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>68500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2000</v>
       </c>
       <c r="G57" s="3">
         <v>2000</v>
       </c>
       <c r="H57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,8 +4260,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4206,65 +4340,68 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E60" s="3">
         <v>12400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,34 +4500,37 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E61" s="3">
         <v>45000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>4100</v>
       </c>
       <c r="J61" s="3">
         <v>4100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -4437,62 +4580,65 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1300</v>
       </c>
       <c r="R62" s="3">
         <v>1300</v>
       </c>
       <c r="S62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,8 +4651,8 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E66" s="3">
         <v>58100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11800</v>
-      </c>
-      <c r="O66" s="3">
-        <v>10000</v>
       </c>
       <c r="P66" s="3">
         <v>10000</v>
       </c>
       <c r="Q66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R66" s="3">
         <v>11300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5056,14 +5224,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>111600</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>77900</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-336300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-309300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-285900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-264400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-247700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-232200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-214800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-196200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-179800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-164600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-147700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-128900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-114700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-102100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-91100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-80000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-51900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-42400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E76" s="3">
         <v>118800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>140500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>160200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>105600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>103300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>118400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>134800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>94200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>109300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>126000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>138300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>158100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>167900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-50000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-40800</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5810,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5895,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-11100</v>
       </c>
       <c r="Q81" s="3">
         <v>-11100</v>
       </c>
       <c r="R81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="S81" s="3">
         <v>-28100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-19700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5854,11 +6053,11 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5866,13 +6065,13 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,8 +6597,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6386,49 +6607,49 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
@@ -6437,10 +6658,10 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,71 +6835,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E94" s="3">
         <v>10400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>13800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>22600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>13100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-99700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1800</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7265,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>69700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>23600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>20100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>4200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>68300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>118900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>31900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>23000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>22900</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7108,23 +7357,23 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
@@ -7134,8 +7383,8 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -7149,8 +7398,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -7176,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>29200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,109 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,31 +772,34 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -851,8 +855,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -931,8 +938,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,74 +1054,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E12" s="3">
         <v>21800</v>
       </c>
-      <c r="E12" s="3">
-        <v>19100</v>
-      </c>
       <c r="F12" s="3">
-        <v>18000</v>
+        <v>18900</v>
       </c>
       <c r="G12" s="3">
+        <v>18500</v>
+      </c>
+      <c r="H12" s="3">
         <v>13300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4100</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,31 +1218,34 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1281,31 +1301,34 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,74 +1414,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E17" s="3">
         <v>27700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16400</v>
       </c>
-      <c r="I17" s="3">
-        <v>18400</v>
-      </c>
       <c r="J17" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K17" s="3">
         <v>19500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5200</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,74 +1495,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-24900</v>
       </c>
       <c r="E18" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-24300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-18400</v>
-      </c>
       <c r="J18" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-19500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-20800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1578,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,41 +1611,42 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1620,32 +1654,32 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,74 +1692,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-24700</v>
       </c>
       <c r="E21" s="3">
-        <v>-21800</v>
+        <v>-27500</v>
       </c>
       <c r="F21" s="3">
-        <v>-21300</v>
+        <v>-24200</v>
       </c>
       <c r="G21" s="3">
-        <v>-16400</v>
+        <v>-22600</v>
       </c>
       <c r="H21" s="3">
-        <v>-15400</v>
+        <v>-17800</v>
       </c>
       <c r="I21" s="3">
-        <v>-17200</v>
+        <v>-16200</v>
       </c>
       <c r="J21" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-18300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-28100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-19600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,8 +1775,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1747,28 +1787,28 @@
         <v>1400</v>
       </c>
       <c r="E22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>300</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1818,74 +1858,77 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-11100</v>
       </c>
       <c r="R23" s="3">
         <v>-11100</v>
       </c>
       <c r="S23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T23" s="3">
         <v>-28100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-19700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,31 +1941,34 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,74 +2107,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-11100</v>
       </c>
       <c r="R26" s="3">
         <v>-11100</v>
       </c>
       <c r="S26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T26" s="3">
         <v>-28100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-19700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5000</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,74 +2190,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-11100</v>
       </c>
       <c r="R27" s="3">
         <v>-11100</v>
       </c>
       <c r="S27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T27" s="3">
         <v>-28100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-19700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2273,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,41 +2605,44 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-1300</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2580,32 +2650,32 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,74 +2688,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-11100</v>
       </c>
       <c r="R33" s="3">
         <v>-11100</v>
       </c>
       <c r="S33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T33" s="3">
         <v>-28100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-19700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2771,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,74 +2854,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-11100</v>
       </c>
       <c r="R35" s="3">
         <v>-11100</v>
       </c>
       <c r="S35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T35" s="3">
         <v>-28100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-19700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,79 +2937,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3025,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,68 +3089,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E41" s="3">
         <v>15200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>40800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>59900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>50900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,68 +3170,71 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E42" s="3">
         <v>129300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>154000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>145500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>81900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>95000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>97400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>88900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>65800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>88500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>98100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>111200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>128600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>119700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>99600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>18900</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,8 +3253,11 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3174,20 +3267,20 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>100</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3196,10 +3289,10 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
@@ -3211,19 +3304,19 @@
         <v>100</v>
       </c>
       <c r="R43" s="3">
+        <v>100</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
@@ -3243,31 +3336,34 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3323,68 +3419,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>8400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>8200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,68 +3502,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E46" s="3">
         <v>153000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>174300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>196300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>200900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>143600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>134100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>131400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>145900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>153700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>100600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>115300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>130600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>141000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>148000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>151000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>164000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>64700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>41300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,31 +3585,34 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3528,16 +3633,16 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>2500</v>
-      </c>
-      <c r="R47" s="3">
-        <v>12200</v>
       </c>
       <c r="S47" s="3">
         <v>12200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>12200</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3554,8 +3659,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3563,68 +3668,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,8 +4000,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3892,16 +4012,16 @@
         <v>800</v>
       </c>
       <c r="E52" s="3">
+        <v>800</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2000</v>
       </c>
       <c r="G52" s="3">
         <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="I52" s="3">
         <v>4200</v>
@@ -3919,32 +4039,32 @@
         <v>4200</v>
       </c>
       <c r="N52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O52" s="3">
         <v>3800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>2400</v>
       </c>
       <c r="P52" s="3">
         <v>2400</v>
       </c>
       <c r="Q52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R52" s="3">
         <v>3300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,68 +4166,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E54" s="3">
         <v>155700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>176900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>200800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>205700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>141800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>139200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>154000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>162000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>123500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>148300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>158900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>169400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>179000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>68500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,68 +4313,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2000</v>
       </c>
       <c r="H57" s="3">
         <v>2000</v>
       </c>
       <c r="I57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,31 +4394,34 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4343,68 +4477,71 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>12000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>10200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>10300</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="L59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="N59" s="3">
         <v>10100</v>
       </c>
-      <c r="I59" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>12200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>11700</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
-        <v>10100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,68 +4560,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E60" s="3">
         <v>15500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,37 +4643,40 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45300</v>
+        <v>42200</v>
       </c>
       <c r="E61" s="3">
-        <v>45000</v>
+        <v>45800</v>
       </c>
       <c r="F61" s="3">
-        <v>44800</v>
+        <v>45700</v>
       </c>
       <c r="G61" s="3">
-        <v>32100</v>
+        <v>45700</v>
       </c>
       <c r="H61" s="3">
-        <v>31900</v>
+        <v>33200</v>
       </c>
       <c r="I61" s="3">
-        <v>24200</v>
+        <v>33300</v>
       </c>
       <c r="J61" s="3">
-        <v>4100</v>
+        <v>25800</v>
       </c>
       <c r="K61" s="3">
         <v>4100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -4583,65 +4726,68 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1600</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>1900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1300</v>
       </c>
       <c r="S62" s="3">
         <v>1300</v>
       </c>
       <c r="T62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4654,8 +4800,8 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,68 +5058,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E66" s="3">
         <v>61300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>58100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11800</v>
-      </c>
-      <c r="P66" s="3">
-        <v>10000</v>
       </c>
       <c r="Q66" s="3">
         <v>10000</v>
       </c>
       <c r="R66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S66" s="3">
         <v>11300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5227,14 +5395,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>111600</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>77900</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,68 +5504,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-360900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-336300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-309300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-285900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-264400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-247700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-232200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-214800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-196200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-179800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-164600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-147700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-128900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-114700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-102100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-91100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-80000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-51900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-42400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,68 +5836,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E76" s="3">
         <v>94400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>118800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>140500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>160200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>105600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>103300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>118400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>134800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>94200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>109300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>126000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>148900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>158100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>167900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-50000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-40800</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,79 +6002,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,74 +6090,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-11100</v>
       </c>
       <c r="R81" s="3">
         <v>-11100</v>
       </c>
       <c r="S81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="T81" s="3">
         <v>-28100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-19700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6173,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6056,11 +6255,11 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -6068,13 +6267,13 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,8 +6818,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6610,49 +6831,49 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
@@ -6661,10 +6882,10 @@
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7065,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E94" s="3">
         <v>17800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-44600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>22600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>13100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-99700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1800</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,31 +7181,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7511,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>69700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>23600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>20100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>4200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>68300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>118900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>31900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>23000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>22900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,23 +7594,26 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>-200</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
@@ -7372,11 +7621,11 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
@@ -7386,8 +7635,8 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -7401,8 +7650,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-31800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>29200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,113 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -775,8 +775,11 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,8 +804,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -858,8 +861,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -941,8 +947,11 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1024,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,77 +1067,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E12" s="3">
         <v>19900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18900</v>
       </c>
-      <c r="G12" s="3">
-        <v>18500</v>
-      </c>
       <c r="H12" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I12" s="3">
         <v>13300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4100</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,8 +1237,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1244,12 +1263,12 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1304,8 +1323,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1331,7 +1353,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1387,8 +1409,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,77 +1440,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E17" s="3">
         <v>24900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,77 +1524,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-20800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,23 +1644,24 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1639,17 +1672,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1657,32 +1690,32 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>200</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,77 +1728,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-27500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-28100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,8 +1814,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1790,28 +1829,28 @@
         <v>1400</v>
       </c>
       <c r="F22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
-        <v>1200</v>
-      </c>
       <c r="H22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1861,77 +1900,80 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-11100</v>
       </c>
       <c r="S23" s="3">
         <v>-11100</v>
       </c>
       <c r="T23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U23" s="3">
         <v>-28100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,8 +1986,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1970,8 +2015,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2027,8 +2072,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,77 +2158,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-11100</v>
       </c>
       <c r="S26" s="3">
         <v>-11100</v>
       </c>
       <c r="T26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U26" s="3">
         <v>-28100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-19700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,77 +2244,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-11100</v>
       </c>
       <c r="S27" s="3">
         <v>-11100</v>
       </c>
       <c r="T27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U27" s="3">
         <v>-28100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-19700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,23 +2674,26 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2635,17 +2704,17 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2653,32 +2722,32 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,77 +2760,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-11100</v>
       </c>
       <c r="S33" s="3">
         <v>-11100</v>
       </c>
       <c r="T33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U33" s="3">
         <v>-28100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,77 +2932,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-11100</v>
       </c>
       <c r="S35" s="3">
         <v>-11100</v>
       </c>
       <c r="T35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U35" s="3">
         <v>-28100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,82 +3018,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,71 +3175,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E41" s="3">
         <v>24600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>62600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>28000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>59900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>50900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,71 +3259,74 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E42" s="3">
         <v>107000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>129300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>145500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>154000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>145500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>81900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>95000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>97400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>65800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>88500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>98100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>111200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>128600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>119700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>99600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>18900</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3256,13 +3345,16 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>500</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -3270,20 +3362,20 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>100</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -3292,10 +3384,10 @@
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
@@ -3307,19 +3399,19 @@
         <v>100</v>
       </c>
       <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
@@ -3339,8 +3431,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3365,8 +3460,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3422,8 +3517,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3448,45 +3546,45 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,71 +3603,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E46" s="3">
         <v>140900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>153000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>174300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>196300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>200900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>143600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>134100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>131400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>145900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>153700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>100600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>115300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>130600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>141000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>148000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>151000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>164000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>64700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>41300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3689,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3614,8 +3718,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3636,16 +3740,16 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>2500</v>
-      </c>
-      <c r="S47" s="3">
-        <v>12200</v>
       </c>
       <c r="T47" s="3">
         <v>12200</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>12200</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3662,8 +3766,8 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3671,71 +3775,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +3861,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3837,8 +3947,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,28 +4119,31 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
         <v>800</v>
       </c>
       <c r="F52" s="3">
+        <v>800</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2000</v>
       </c>
       <c r="H52" s="3">
         <v>2000</v>
       </c>
       <c r="I52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="J52" s="3">
         <v>4200</v>
@@ -4042,32 +4161,32 @@
         <v>4200</v>
       </c>
       <c r="O52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P52" s="3">
         <v>3800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>2400</v>
       </c>
       <c r="Q52" s="3">
         <v>2400</v>
       </c>
       <c r="R52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S52" s="3">
         <v>3300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4205,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,71 +4291,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E54" s="3">
         <v>143400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>155700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>176900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>200800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>205700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>150900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>141800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>139200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>154000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>162000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>123500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>148300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>158900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>169400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>179000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>68500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,71 +4443,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2000</v>
       </c>
       <c r="I57" s="3">
         <v>2000</v>
       </c>
       <c r="J57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,19 +4527,22 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>900</v>
       </c>
       <c r="G58" s="3">
         <v>900</v>
@@ -4421,11 +4554,11 @@
         <v>900</v>
       </c>
       <c r="J58" s="3">
+        <v>900</v>
+      </c>
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4480,8 +4613,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4506,45 +4642,45 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>12200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,71 +4699,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E60" s="3">
         <v>18300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,40 +4785,43 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E61" s="3">
         <v>42200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>45700</v>
       </c>
       <c r="G61" s="3">
         <v>45700</v>
       </c>
       <c r="H61" s="3">
+        <v>45700</v>
+      </c>
+      <c r="I61" s="3">
         <v>33200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>4100</v>
       </c>
       <c r="L61" s="3">
         <v>4100</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -4729,8 +4871,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4752,45 +4897,45 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>1900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1300</v>
       </c>
       <c r="T62" s="3">
         <v>1300</v>
       </c>
       <c r="U62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4803,8 +4948,8 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4812,8 +4957,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,71 +5215,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E66" s="3">
         <v>60600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11800</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>10000</v>
       </c>
       <c r="R66" s="3">
         <v>10000</v>
       </c>
       <c r="S66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="T66" s="3">
         <v>11300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5398,14 +5565,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>111600</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>77900</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,71 +5677,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-388000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-360900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-336300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-309300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-285900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-264400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-247700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-232200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-214800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-196200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-179800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-147700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-128900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-114700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-102100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-91100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-80000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-51900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-42400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,71 +6021,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E76" s="3">
         <v>82800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>118800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>140500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>160200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>105600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>103300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>134800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>149200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>94200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>109300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>138300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>158100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>167900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-50000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-40800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,82 +6193,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6093,77 +6284,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-11100</v>
       </c>
       <c r="S81" s="3">
         <v>-11100</v>
       </c>
       <c r="T81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="U81" s="3">
         <v>-28100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6176,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,8 +6404,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6258,11 +6456,11 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -6270,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -6290,8 +6488,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,77 +6918,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,8 +7038,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6834,49 +7054,49 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
@@ -6885,10 +7105,10 @@
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -6902,8 +7122,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,77 +7294,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E94" s="3">
         <v>23300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>22600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>19700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-99700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7151,8 +7380,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7208,8 +7441,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7265,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,77 +7756,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>10500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>69700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>23600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>20100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>68300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>118900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>31900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>23000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>22900</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,26 +7842,29 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
@@ -7624,11 +7872,11 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
@@ -7638,8 +7886,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -7653,8 +7901,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -7680,77 +7928,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E102" s="3">
         <v>9300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-31800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>29200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="92">
   <si>
     <t>INZY</t>
   </si>
@@ -656,116 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,8 +779,11 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -807,8 +811,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -864,8 +868,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -950,8 +957,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1036,8 +1046,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,80 +1081,81 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E12" s="3">
         <v>23000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21800</v>
       </c>
-      <c r="G12" s="3">
-        <v>18900</v>
-      </c>
       <c r="H12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="I12" s="3">
         <v>18000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>25200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1168,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,13 +1257,16 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1266,12 +1286,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1326,8 +1346,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1356,7 +1379,7 @@
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1412,8 +1435,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,80 +1467,81 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E17" s="3">
         <v>27200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5200</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1527,80 +1554,83 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-27200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-24300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-28300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1643,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,26 +1678,27 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1675,17 +1709,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1693,32 +1727,32 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>200</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>200</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,80 +1765,83 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-27000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-27500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-12400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-28100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,8 +1854,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1832,28 +1872,28 @@
         <v>1400</v>
       </c>
       <c r="G22" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H22" s="3">
         <v>1300</v>
       </c>
       <c r="I22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1903,80 +1943,83 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-11100</v>
       </c>
       <c r="T23" s="3">
         <v>-11100</v>
       </c>
       <c r="U23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V23" s="3">
         <v>-28100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,8 +2032,11 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2018,8 +2064,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2075,8 +2121,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,80 +2210,83 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-11100</v>
       </c>
       <c r="T26" s="3">
         <v>-11100</v>
       </c>
       <c r="U26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V26" s="3">
         <v>-28100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,80 +2299,83 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-11100</v>
       </c>
       <c r="T27" s="3">
         <v>-11100</v>
       </c>
       <c r="U27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V27" s="3">
         <v>-28100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2388,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2477,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2566,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2655,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,26 +2744,29 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2707,17 +2777,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2725,32 +2795,32 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-200</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,80 +2833,83 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-11100</v>
       </c>
       <c r="T33" s="3">
         <v>-11100</v>
       </c>
       <c r="U33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V33" s="3">
         <v>-28100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2849,8 +2922,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,80 +3011,83 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-11100</v>
       </c>
       <c r="T35" s="3">
         <v>-11100</v>
       </c>
       <c r="U35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V35" s="3">
         <v>-28100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3021,85 +3100,88 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3194,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3229,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,74 +3262,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E41" s="3">
         <v>21100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>62600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>59900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>50900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3262,74 +3349,77 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E42" s="3">
         <v>92000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>107000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>129300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>145500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>154000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>145500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>81900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>95000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>97400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>88900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>65800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>88500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>98100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>111200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>128600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>119700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>99600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>13000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18900</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,37 +3438,40 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>100</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3387,10 +3480,10 @@
         <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
@@ -3402,19 +3495,19 @@
         <v>100</v>
       </c>
       <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3434,8 +3527,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3463,8 +3559,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3520,8 +3616,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3549,45 +3648,45 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,74 +3705,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E46" s="3">
         <v>120700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>140900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>153000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>174300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>196300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>200900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>143600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>134100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>131400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>145900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>153700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>100600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>115300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>130600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>141000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>148000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>151000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>164000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>64700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>41300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3692,8 +3794,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3721,8 +3826,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3743,16 +3848,16 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>2500</v>
-      </c>
-      <c r="T47" s="3">
-        <v>12200</v>
       </c>
       <c r="U47" s="3">
         <v>12200</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>12200</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3769,8 +3874,8 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3778,74 +3883,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3972,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3950,8 +4061,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4150,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,31 +4239,34 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>800</v>
       </c>
       <c r="F52" s="3">
         <v>800</v>
       </c>
       <c r="G52" s="3">
+        <v>800</v>
+      </c>
+      <c r="H52" s="3">
         <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2000</v>
       </c>
       <c r="I52" s="3">
         <v>2000</v>
       </c>
       <c r="J52" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="K52" s="3">
         <v>4200</v>
@@ -4164,32 +4284,32 @@
         <v>4200</v>
       </c>
       <c r="P52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>2400</v>
       </c>
       <c r="R52" s="3">
         <v>2400</v>
       </c>
       <c r="S52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T52" s="3">
         <v>3300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,8 +4328,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,74 +4417,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E54" s="3">
         <v>123200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>143400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>155700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>176900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>200800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>205700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>150900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>141800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>139200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>154000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>162000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>123500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>148300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>158900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>169400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>179000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>68500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4380,8 +4506,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4541,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,74 +4574,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2000</v>
       </c>
       <c r="J57" s="3">
         <v>2000</v>
       </c>
       <c r="K57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,22 +4661,25 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E58" s="3">
         <v>15400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>900</v>
       </c>
       <c r="H58" s="3">
         <v>900</v>
@@ -4557,11 +4691,11 @@
         <v>900</v>
       </c>
       <c r="K58" s="3">
+        <v>900</v>
+      </c>
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4616,8 +4750,11 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4645,45 +4782,45 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,74 +4839,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E60" s="3">
         <v>33900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,43 +4928,46 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E61" s="3">
         <v>31500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>45700</v>
       </c>
       <c r="H61" s="3">
         <v>45700</v>
       </c>
       <c r="I61" s="3">
+        <v>45700</v>
+      </c>
+      <c r="J61" s="3">
         <v>33200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>33300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>4100</v>
       </c>
       <c r="M61" s="3">
         <v>4100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -4874,8 +5017,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4900,45 +5046,45 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1300</v>
       </c>
       <c r="U62" s="3">
         <v>1300</v>
       </c>
       <c r="V62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4951,8 +5097,8 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -4960,8 +5106,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5195,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5284,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,74 +5373,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E66" s="3">
         <v>65400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>58100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11800</v>
-      </c>
-      <c r="R66" s="3">
-        <v>10000</v>
       </c>
       <c r="S66" s="3">
         <v>10000</v>
       </c>
       <c r="T66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="U66" s="3">
         <v>11300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5304,8 +5462,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5497,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5584,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5673,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5568,14 +5736,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>111600</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>77900</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5594,8 +5762,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,74 +5851,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-416000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-388000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-360900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-336300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-285900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-264400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-247700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-232200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-214800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-196200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-179800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-147700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-128900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-114700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-102100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-91100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-80000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-51900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-42400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5766,8 +5940,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6029,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6118,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,74 +6207,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E76" s="3">
         <v>57800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>82800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>94400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>140500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>105600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>103300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>134800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>149200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>94200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>109300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>126000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>138300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>148900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>158100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>167900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-50000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-40800</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6110,8 +6296,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,85 +6385,88 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6287,80 +6479,83 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12500</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-11100</v>
       </c>
       <c r="T81" s="3">
         <v>-11100</v>
       </c>
       <c r="U81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="V81" s="3">
         <v>-28100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6373,8 +6568,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,8 +6603,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6459,11 +6658,11 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -6471,13 +6670,13 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6491,8 +6690,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6779,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6868,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6957,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7046,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,80 +7135,83 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7007,8 +7224,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,13 +7259,14 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7057,49 +7278,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
@@ -7108,10 +7329,10 @@
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -7125,8 +7346,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7435,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,80 +7524,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E94" s="3">
         <v>15400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>23300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>22600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>13100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-99700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7383,8 +7613,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,8 +7648,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7444,8 +7678,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7501,8 +7735,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7824,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7913,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,80 +8002,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>69700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>4200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>68300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>118900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>31900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>23000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>22900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7845,29 +8091,32 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -7875,11 +8124,11 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
@@ -7889,8 +8138,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -7904,8 +8153,8 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7931,80 +8180,83 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-31800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>29200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>19400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8015,6 +8267,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
